--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486773_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486773_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6065</v>
+        <v>5.186</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5381</v>
+        <v>4.8693</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0684</v>
+        <v>0.3167</v>
       </c>
       <c r="G2" t="n">
         <v>3.3931</v>
@@ -610,13 +610,13 @@
         <v>0.5792</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0203</v>
+        <v>0.5999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9927</v>
+        <v>0.3239</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0277</v>
+        <v>0.276</v>
       </c>
       <c r="V2" t="n">
         <v>0.6138</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5059</v>
+        <v>0.8961</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3178</v>
+        <v>1.0556</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1881</v>
+        <v>-0.1595</v>
       </c>
       <c r="G3" t="n">
         <v>-3.8754</v>
@@ -688,13 +688,13 @@
         <v>0.9654</v>
       </c>
       <c r="S3" t="n">
-        <v>0.127</v>
+        <v>0.5172</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.214</v>
+        <v>-0.4762</v>
       </c>
       <c r="U3" t="n">
-        <v>1.341</v>
+        <v>0.9933</v>
       </c>
       <c r="V3" t="n">
         <v>4.2543</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4477</v>
+        <v>0.3567</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2475</v>
+        <v>0.2062</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2002</v>
+        <v>0.1505</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6506</v>
@@ -766,13 +766,13 @@
         <v>0.9654</v>
       </c>
       <c r="S4" t="n">
-        <v>1.539</v>
+        <v>1.4481</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3305</v>
+        <v>0.2892</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2085</v>
+        <v>1.1589</v>
       </c>
       <c r="V4" t="n">
         <v>2.4554</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4427</v>
+        <v>-1.0344</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2032</v>
+        <v>-0.3479</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2395</v>
+        <v>-0.6865</v>
       </c>
       <c r="G5" t="n">
         <v>1.1958</v>
@@ -844,13 +844,13 @@
         <v>1.1585</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9986</v>
+        <v>0.4069</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1383</v>
+        <v>-0.283</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1369</v>
+        <v>0.6899</v>
       </c>
       <c r="V5" t="n">
         <v>-0.8995</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5924</v>
+        <v>-1.5773</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1803</v>
+        <v>0.0335</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4121</v>
+        <v>-1.6108</v>
       </c>
       <c r="G6" t="n">
         <v>1.2118</v>
@@ -922,13 +922,13 @@
         <v>0.7723</v>
       </c>
       <c r="S6" t="n">
-        <v>0.833</v>
+        <v>0.8481</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4693</v>
+        <v>-0.2556</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3023</v>
+        <v>1.1036</v>
       </c>
       <c r="V6" t="n">
         <v>-1.5133</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SOLA ARGEMI</t>
+          <t>M. OLIVA I CAMPABADAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8452</v>
+        <v>-1.8494</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7463</v>
+        <v>-0.3456</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0989</v>
+        <v>-1.5038</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.8708</v>
+        <v>-1.332</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9515</v>
+        <v>-0.9657</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.9193</v>
+        <v>-0.3662</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.6906</v>
+        <v>0.0407</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1232</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5674</v>
+        <v>0.0407</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1802</v>
+        <v>-1.3727</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8283</v>
+        <v>-0.9657</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3519</v>
+        <v>-0.4069</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4464</v>
+        <v>-0.4828</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3305</v>
+        <v>-0.3863</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1159</v>
+        <v>-0.0965</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6138</v>
+        <v>-0.6138</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. OLIVA I CAMPABADAL</t>
+          <t>J. SOLA ARGEMI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9846</v>
+        <v>-1.8988</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4559</v>
+        <v>-1.0979</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5286</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.332</v>
+        <v>-3.8708</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9657</v>
+        <v>-1.9515</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3662</v>
+        <v>-1.9193</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0407</v>
+        <v>-1.6906</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-1.1232</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0407</v>
+        <v>-0.5674</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3727</v>
+        <v>-2.1802</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9657</v>
+        <v>-0.8283</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4069</v>
+        <v>-1.3519</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.618</v>
+        <v>0.3929</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4966</v>
+        <v>-0.0211</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1213</v>
+        <v>0.4139</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6138</v>
+        <v>0.6138</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2644</v>
+        <v>-2.3542</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2948</v>
+        <v>-0.5087</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9697</v>
+        <v>-1.8455</v>
       </c>
       <c r="G9" t="n">
         <v>-2.8408</v>
@@ -1156,13 +1156,13 @@
         <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.331</v>
+        <v>0.5792</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1036</v>
+        <v>-0.3176</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7726</v>
+        <v>0.8968</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2856</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0805</v>
+        <v>-3.635</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0204</v>
+        <v>-2.5997</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0601</v>
+        <v>-1.0353</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0284</v>
@@ -1234,13 +1234,13 @@
         <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1213</v>
+        <v>0.3241</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5518</v>
+        <v>-0.1312</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4305</v>
+        <v>0.4553</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8764</v>
+        <v>-5.2364</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1112</v>
+        <v>-2.794</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7652</v>
+        <v>-2.4424</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7533</v>
@@ -1312,13 +1312,13 @@
         <v>0.5792</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8608</v>
+        <v>-0.2208</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9933</v>
+        <v>-0.6761</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1325</v>
+        <v>0.4553</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8415</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.5261</v>
+        <v>-11.1467</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9087</v>
+        <v>-1.5292</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.6174</v>
+        <v>-9.6175</v>
       </c>
       <c r="G12" t="n">
         <v>-12.5506</v>
@@ -1390,16 +1390,16 @@
         <v>8.688500000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>3.0332</v>
+        <v>4.4128</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.3132</v>
+        <v>-1.934</v>
       </c>
       <c r="U12" t="n">
-        <v>6.3466</v>
+        <v>6.346500000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>2.7836</v>
+        <v>2.783600000000001</v>
       </c>
       <c r="W12" t="n">
         <v>10.3927</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.648400000000001</v>
+        <v>9.9505</v>
       </c>
       <c r="E13" t="n">
-        <v>7.5312</v>
+        <v>7.6346</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1172</v>
+        <v>2.3158</v>
       </c>
       <c r="G13" t="n">
         <v>9.147500000000001</v>
@@ -1468,13 +1468,13 @@
         <v>1.9308</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.255</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0485</v>
+        <v>-0.945</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4914</v>
+        <v>0.6901</v>
       </c>
       <c r="V13" t="n">
         <v>0.2856</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1803</v>
+        <v>2.7418</v>
       </c>
       <c r="E14" t="n">
-        <v>7.1776</v>
+        <v>6.7639</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.9973</v>
+        <v>-4.0221</v>
       </c>
       <c r="G14" t="n">
         <v>2.5045</v>
@@ -1546,13 +1546,13 @@
         <v>1.3515</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1545</v>
+        <v>-0.593</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3038</v>
+        <v>-0.7175</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1493</v>
+        <v>0.1245</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3282</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. GARCIA NAVARO</t>
+          <t>M. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.75</v>
+        <v>2.1427</v>
       </c>
       <c r="E15" t="n">
-        <v>1.79</v>
+        <v>-1.167</v>
       </c>
       <c r="F15" t="n">
-        <v>0.96</v>
+        <v>3.3097</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4687</v>
+        <v>0.7014</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0619</v>
+        <v>0.4279</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4068</v>
+        <v>0.2735</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0218</v>
+        <v>-0.829</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0972</v>
+        <v>0.1221</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4469</v>
+        <v>1.5304</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1373</v>
+        <v>1.379</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3096</v>
+        <v>0.1514</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7723</v>
+        <v>1.3515</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9308</v>
+        <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6787</v>
+        <v>0.0897</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.359</v>
+        <v>-0.338</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0377</v>
+        <v>0.4278</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.1698</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ALONSO MENOR</t>
+          <t>D. GARCIA NAVARO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7165</v>
+        <v>2.1128</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2704</v>
+        <v>1.3763</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9869</v>
+        <v>0.7365</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7014</v>
+        <v>3.4687</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4279</v>
+        <v>0.0619</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2735</v>
+        <v>3.4068</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.829</v>
+        <v>3.0218</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9510999999999999</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1221</v>
+        <v>3.0972</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5304</v>
+        <v>0.4469</v>
       </c>
       <c r="N16" t="n">
-        <v>1.379</v>
+        <v>0.1373</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1514</v>
+        <v>0.3096</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3515</v>
+        <v>0.7723</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3515</v>
+        <v>1.9308</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3365</v>
+        <v>0.0416</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4415</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.105</v>
+        <v>0.8142</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-2.1698</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4044</v>
+        <v>1.6609</v>
       </c>
       <c r="E17" t="n">
-        <v>0.255</v>
+        <v>0.4618</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1493</v>
+        <v>1.199</v>
       </c>
       <c r="G17" t="n">
         <v>0.7503</v>
@@ -1780,13 +1780,13 @@
         <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3806</v>
+        <v>-0.1241</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7174</v>
+        <v>-0.5105</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3368</v>
+        <v>0.3865</v>
       </c>
       <c r="V17" t="n">
         <v>1.2277</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ESTEBANEZ ESCUDERO</t>
+          <t>L. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0114</v>
+        <v>0.1058</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0405</v>
+        <v>0.534</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0518</v>
+        <v>-0.4282</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1258</v>
+        <v>-0.5079</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0136</v>
+        <v>0.8689</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1394</v>
+        <v>-1.3768</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4198</v>
+        <v>1.0376</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4966</v>
+        <v>1.076</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0384</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5456</v>
+        <v>-1.5454</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.483</v>
+        <v>-0.2071</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0626</v>
+        <v>-1.3384</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2371</v>
+        <v>-0.5448</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.607</v>
+        <v>-0.5036</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3699</v>
+        <v>-0.0412</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. ALONSO MENOR</t>
+          <t>S. HERTEL HERMOSA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0224</v>
+        <v>-0.0353</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4306</v>
+        <v>0.0269</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.453</v>
+        <v>-0.0622</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5079</v>
+        <v>-0.256</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8689</v>
+        <v>-0.1655</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3768</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0376</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>1.076</v>
+        <v>0.0414</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0384</v>
+        <v>0.0407</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5454</v>
+        <v>-0.3381</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2071</v>
+        <v>-0.2069</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3384</v>
+        <v>-0.1311</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.673</v>
+        <v>0.0276</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.607</v>
+        <v>-0.0552</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.066</v>
+        <v>0.0828</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. HERTEL HERMOSA</t>
+          <t>M. ESTEBANEZ ESCUDERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0569</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0269</v>
+        <v>1.1439</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1119</v>
+        <v>-1.2008</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.256</v>
+        <v>-1.1258</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1655</v>
+        <v>0.0136</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-1.1394</v>
       </c>
       <c r="J20" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.4198</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0414</v>
+        <v>0.4966</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0407</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3381</v>
+        <v>-1.5456</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2069</v>
+        <v>-0.483</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1311</v>
+        <v>-1.0626</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0221</v>
+        <v>-0.2827</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0552</v>
+        <v>-0.5036</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0331</v>
+        <v>0.2209</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="21">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.489</v>
+        <v>-1.5883</v>
       </c>
       <c r="E22" t="n">
         <v>0.4536</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9426</v>
+        <v>-2.0419</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6366000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>0.3862</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0109</v>
+        <v>-0.1102</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2759</v>
       </c>
       <c r="U22" t="n">
-        <v>0.265</v>
+        <v>0.1657</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2277</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5788</v>
+        <v>-3.521</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.3749</v>
+        <v>-7.1681</v>
       </c>
       <c r="F23" t="n">
-        <v>3.7961</v>
+        <v>3.6471</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9145</v>
@@ -2248,13 +2248,13 @@
         <v>2.3169</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5404</v>
+        <v>-0.4826</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.214</v>
+        <v>-1.0072</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6736</v>
+        <v>0.5246</v>
       </c>
       <c r="V23" t="n">
         <v>0.6138</v>
@@ -2284,7 +2284,7 @@
         <v>12.5262</v>
       </c>
       <c r="E24" t="n">
-        <v>9.617600000000003</v>
+        <v>9.617400000000004</v>
       </c>
       <c r="F24" t="n">
         <v>2.9086</v>
@@ -2326,13 +2326,13 @@
         <v>14.4808</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.0332</v>
+        <v>-3.0333</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.3467</v>
+        <v>-6.3466</v>
       </c>
       <c r="U24" t="n">
-        <v>3.3133</v>
+        <v>3.3134</v>
       </c>
       <c r="V24" t="n">
         <v>-2.7837</v>
